--- a/backtest_runs/20260410_193731/by_symbol/PSEL/PSEL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PSEL/PSEL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-2228.850000000008</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>106161.22</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>108812.44</v>
@@ -817,7 +817,7 @@
         <v>-26.91000000000213</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>108785.53</v>
@@ -909,7 +909,7 @@
         <v>-4587.570000000004</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>109417.33</v>
@@ -1047,7 +1047,7 @@
         <v>-859.9500000000027</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>109247.68</v>
@@ -1093,7 +1093,7 @@
         <v>-972.2699999999936</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>108275.41</v>
@@ -1185,7 +1185,7 @@
         <v>-889.2000000000027</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>107874.1</v>
@@ -1231,7 +1231,7 @@
         <v>-2810.339999999998</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>105063.76</v>
@@ -1415,7 +1415,7 @@
         <v>-308.8800000000117</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>108560.89</v>
@@ -1461,7 +1461,7 @@
         <v>-2256.929999999996</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>106303.96</v>
@@ -1645,7 +1645,7 @@
         <v>-1091.610000000005</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>110200.06</v>
